--- a/Thesis_TSSP_NEWNEW_M1_Results_5_Scenarios.xlsx
+++ b/Thesis_TSSP_NEWNEW_M1_Results_5_Scenarios.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -520,12 +520,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
     </row>
@@ -547,17 +547,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,12 +584,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 10:28</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -611,12 +611,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 10:56</t>
+          <t>4/5/2026 14:51</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:22</t>
+          <t>4/5/2026 10:34</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -722,22 +722,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 15:31</t>
+          <t>4/5/2026 15:29</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 10:24</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:38</t>
+          <t>4/5/2026 10:39</t>
         </is>
       </c>
     </row>
@@ -796,27 +796,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 15:26</t>
+          <t>4/5/2026 15:29</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 08:23</t>
+          <t>4/5/2026 14:21</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 15:32</t>
+          <t>4/5/2026 08:05</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -870,27 +870,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 08:28</t>
+          <t>4/5/2026 14:18</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 15:05</t>
+          <t>4/5/2026 14:05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -927,12 +927,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
     </row>
@@ -944,27 +944,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:30</t>
+          <t>4/5/2026 15:21</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1092,32 +1092,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 14:27</t>
+          <t>4/5/2026 10:10</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 14:32</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
     </row>
@@ -1129,32 +1129,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
     </row>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 13:50</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 15:28</t>
+          <t>4/5/2026 14:13</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1203,22 +1203,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 13:48</t>
+          <t>4/5/2026 13:37</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 15:03</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.88 min</t>
+          <t>32.02 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>86.80 min</t>
+          <t>90.20 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>93.00 min</t>
+          <t>110.00 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21.00 min</t>
+          <t>13.40 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8.80/5.60/7.40 min</t>
+          <t>4.00/3.20/6.60 min</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>30.1160 sec</t>
+          <t>41.2380 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.5109 %</t>
+          <t>0.9605 %</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>36.00 min | 93.00 min</t>
+          <t>36.10 min | 110.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>31.00 min | 86.00 min</t>
+          <t>28.81 min | 86.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>30.71 min | 83.00 min</t>
+          <t>30.48 min | 83.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>34.19 min | 82.00 min</t>
+          <t>32.38 min | 82.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>32.48 min | 90.00 min</t>
+          <t>32.33 min | 90.00 min</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>13.98</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="36">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>9.32</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="38">
@@ -1607,7 +1607,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11.65</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="39">
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3.63</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="40">
@@ -1627,7 +1627,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2.73</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="41">
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3.18</v>
+        <v>4.54</v>
       </c>
     </row>
     <row r="42">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>31.59</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="43">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>22.57</v>
+        <v>27.08</v>
       </c>
     </row>
     <row r="44">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>40.62</v>
+        <v>45.13</v>
       </c>
     </row>
   </sheetData>
@@ -1772,48 +1772,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4/5/2026 08:54</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1845,35 +1845,35 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/5/2026 09:42</t>
+          <t>4/5/2026 09:59</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 11:03</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:39</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -2312,48 +2312,48 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:32</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:34</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:36</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>4/5/2026 07:31</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>4/5/2026 07:46</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4/5/2026 08:01</t>
-        </is>
-      </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="N11" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2492,48 +2492,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:44</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:58</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
@@ -2818,22 +2818,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>4/5/2026 10:03</t>
+          <t>4/5/2026 09:58</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="N19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -2878,22 +2878,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 10:43</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -2912,48 +2912,48 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:52</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>71</v>
+        <v>51</v>
       </c>
       <c r="N21" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -3478,22 +3478,22 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:21</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:39</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="N30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3572,25 +3572,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:07</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:11</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:11</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -3598,22 +3598,22 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -3692,25 +3692,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:35</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -3718,22 +3718,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:35</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -3898,22 +3898,22 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>4/5/2026 07:22</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>4/5/2026 07:29</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>4/5/2026 07:36</t>
-        </is>
-      </c>
       <c r="L37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N37" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4078,22 +4078,22 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:40</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>4/5/2026 10:00</t>
+          <t>4/5/2026 09:54</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -4112,48 +4112,48 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 08:59</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 08:59</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4/5/2026 09:49</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M41" t="n">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="N41" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -4498,22 +4498,22 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4/5/2026 13:23</t>
+          <t>4/5/2026 13:24</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M47" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -4952,25 +4952,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:29</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:33</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -4978,22 +4978,22 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:33</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:00</t>
         </is>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="N55" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -5338,22 +5338,22 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -5805,35 +5805,35 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>4/5/2026 09:12</t>
         </is>
       </c>
-      <c r="I69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:12</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5972,48 +5972,48 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>4/5/2026 09:20</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:29</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:29</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
           <t>4/5/2026 09:30</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:39</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>10</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:46</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:47</t>
-        </is>
-      </c>
       <c r="I72" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:11</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="N72" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -6058,22 +6058,22 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:38</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>4/5/2026 08:20</t>
+          <t>4/5/2026 08:16</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:36</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="N75" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6418,22 +6418,22 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 07:21</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>4/5/2026 07:32</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="N79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -6478,22 +6478,22 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M80" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -6645,16 +6645,16 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:19</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M83" t="n">
         <v>50</v>
@@ -6778,22 +6778,22 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N85" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6898,22 +6898,22 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:08</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M87" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
@@ -7065,35 +7065,35 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>4/5/2026 09:11</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t>4/5/2026 09:12</t>
         </is>
       </c>
-      <c r="I90" t="n">
-        <v>1</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:12</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>4/5/2026 09:13</t>
-        </is>
-      </c>
       <c r="L90" t="n">
         <v>0</v>
       </c>
       <c r="M90" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7198,22 +7198,22 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:24</t>
+          <t>4/5/2026 07:23</t>
         </is>
       </c>
       <c r="L92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -7532,48 +7532,48 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 08:58</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4/5/2026 09:17</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M98" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M101" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102">
@@ -7858,22 +7858,22 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:41</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 09:58</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="N103" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -7952,48 +7952,48 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:51</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>4/5/2026 09:41</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="L105" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="N105" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
